--- a/products/Professional_Services_Inquiry_AI_Kit_v0.1.xlsx
+++ b/products/Professional_Services_Inquiry_AI_Kit_v0.1.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start" sheetId="1" r:id="Rc6e13396767d4ef9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inquiry Intake" sheetId="2" r:id="R875cdcc093474731"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Triage Rules" sheetId="3" r:id="R9a3c87423cbc4152"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consult Prep" sheetId="4" r:id="R7ee87de2685548d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reply Builder" sheetId="5" r:id="Rf167928bacc448dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Boundary Check" sheetId="6" r:id="Ra87df3cf4e9b42be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Pack" sheetId="7" r:id="R4cae56144ffe4f21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="はじめに" sheetId="1" r:id="Rd21acbb10f1043f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="相談内容入力" sheetId="2" r:id="Rdfbf13ecb91742d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="振り分けルール" sheetId="3" r:id="Rcec8a6f8b6fe43d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="相談準備" sheetId="4" r:id="R5edb9d941e3a4903"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="返信作成" sheetId="5" r:id="R46396291b3804542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI境界チェック" sheetId="6" r:id="Rb7b29db57e25479d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロンプト集" sheetId="7" r:id="R8be059ff15704f6d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -249,51 +249,58 @@
       </x:c>
       <x:c r="B1" s="7"/>
     </x:row>
-    <x:row r="2" ht="33" customHeight="1"/>
+    <x:row r="2" ht="33" customHeight="1">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+    </x:row>
     <x:row r="3" ht="33" customHeight="1">
       <x:c r="A3" s="5" t="str">
         <x:v>弁護士、税理士、社労士、行政書士、コンサルなどが、専門判断をAIに任せず、問い合わせ内容を整理し、初回相談前の確認事項と返信案を作るためのテンプレートです。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" ht="33" customHeight="1"/>
+      <x:c r="B3"/>
+    </x:row>
+    <x:row r="4" ht="33" customHeight="1">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+    </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
-        <x:v>Step 1</x:v>
+        <x:v>手順 1</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>Inquiry Intakeに相談内容を事実ベースで入力</x:v>
+        <x:v>相談内容入力に相談内容を事実ベースで入力</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
-        <x:v>Step 2</x:v>
+        <x:v>手順 2</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>Triage Rulesで受ける/確認/断る/紹介の候補に分類</x:v>
+        <x:v>振り分けルールで受ける/確認/断る/紹介の候補に分類</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
-        <x:v>Step 3</x:v>
+        <x:v>手順 3</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>Consult Prepで初回相談の確認事項を作る</x:v>
+        <x:v>相談準備で初回相談の確認事項を作る</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
-        <x:v>Step 4</x:v>
+        <x:v>手順 4</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>Reply Builderで返信案を作り、人間が責任を持って修正</x:v>
+        <x:v>返信 作成で返信案を作り、人間が責任を持って修正</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
-        <x:v>Step 5</x:v>
+        <x:v>手順 5</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>AI Boundary Checkで専門判断、価格、契約条件をAIに断定させない</x:v>
+        <x:v>AI境界チェックで専門判断、価格、契約条件をAIに断定させない</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
@@ -338,49 +345,49 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Field</x:v>
+        <x:v>項目</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Value</x:v>
+        <x:v>入力欄</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Required</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Example</x:v>
+        <x:v>例</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>AI Can Draft?</x:v>
+        <x:v>AIが下書き可?</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Human Must Verify?</x:v>
+        <x:v>人の確認必須?</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Risk If Wrong</x:v>
+        <x:v>間違えた時のリスク</x:v>
       </x:c>
       <x:c r="H1" s="11" t="str">
-        <x:v>Before Reply</x:v>
+        <x:v>返信前の扱い</x:v>
       </x:c>
       <x:c r="I1" s="11" t="str">
-        <x:v>Notes</x:v>
+        <x:v>メモ</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>相談者名/会社名</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str"/>
+      <x:c r="B2" s="6"/>
       <x:c r="C2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
         <x:v>株式会社サンプル</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
         <x:v>宛名ミス</x:v>
@@ -388,24 +395,24 @@
       <x:c r="H2" s="6" t="str">
         <x:v>確認</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="str"/>
+      <x:c r="I2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>連絡先</x:v>
       </x:c>
-      <x:c r="B3" s="6" t="str"/>
+      <x:c r="B3" s="6"/>
       <x:c r="C3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
         <x:v>email@example.com</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
         <x:v>返信不能</x:v>
@@ -413,24 +420,24 @@
       <x:c r="H3" s="6" t="str">
         <x:v>確認</x:v>
       </x:c>
-      <x:c r="I3" s="6" t="str"/>
+      <x:c r="I3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>相談カテゴリ</x:v>
       </x:c>
-      <x:c r="B4" s="6" t="str"/>
+      <x:c r="B4" s="6"/>
       <x:c r="C4" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
         <x:v>契約書/税務/労務/補助金/業務改善</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str">
         <x:v>担当ミス</x:v>
@@ -438,24 +445,24 @@
       <x:c r="H4" s="6" t="str">
         <x:v>分類</x:v>
       </x:c>
-      <x:c r="I4" s="6" t="str"/>
+      <x:c r="I4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>相談の背景</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="str"/>
+      <x:c r="B5" s="6"/>
       <x:c r="C5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
         <x:v>取引先との契約前に確認したい</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
         <x:v>論点ズレ</x:v>
@@ -463,24 +470,24 @@
       <x:c r="H5" s="6" t="str">
         <x:v>要約</x:v>
       </x:c>
-      <x:c r="I5" s="6" t="str"/>
+      <x:c r="I5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>期限</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="str"/>
+      <x:c r="B6" s="6"/>
       <x:c r="C6" s="6" t="str">
-        <x:v>If any</x:v>
+        <x:v>あれば</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
         <x:v>今週中</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G6" s="6" t="str">
         <x:v>対応不能</x:v>
@@ -488,24 +495,24 @@
       <x:c r="H6" s="6" t="str">
         <x:v>確認</x:v>
       </x:c>
-      <x:c r="I6" s="6" t="str"/>
+      <x:c r="I6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>関係者</x:v>
       </x:c>
-      <x:c r="B7" s="6" t="str"/>
+      <x:c r="B7" s="6"/>
       <x:c r="C7" s="6" t="str">
-        <x:v>If any</x:v>
+        <x:v>あれば</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
         <x:v>自社、取引先、従業員</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
         <x:v>利益相反</x:v>
@@ -513,24 +520,24 @@
       <x:c r="H7" s="6" t="str">
         <x:v>確認</x:v>
       </x:c>
-      <x:c r="I7" s="6" t="str"/>
+      <x:c r="I7" s="6"/>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>金額/規模</x:v>
       </x:c>
-      <x:c r="B8" s="6" t="str"/>
+      <x:c r="B8" s="6"/>
       <x:c r="C8" s="6" t="str">
-        <x:v>If relevant</x:v>
+        <x:v>必要なら</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
         <x:v>月額30万円の契約</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
         <x:v>重要度誤認</x:v>
@@ -538,24 +545,24 @@
       <x:c r="H8" s="6" t="str">
         <x:v>確認</x:v>
       </x:c>
-      <x:c r="I8" s="6" t="str"/>
+      <x:c r="I8" s="6"/>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>資料の有無</x:v>
       </x:c>
-      <x:c r="B9" s="6" t="str"/>
+      <x:c r="B9" s="6"/>
       <x:c r="C9" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
         <x:v>契約書案あり</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G9" s="6" t="str">
         <x:v>準備不足</x:v>
@@ -563,24 +570,24 @@
       <x:c r="H9" s="6" t="str">
         <x:v>依頼</x:v>
       </x:c>
-      <x:c r="I9" s="6" t="str"/>
+      <x:c r="I9" s="6"/>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>希望する結果</x:v>
       </x:c>
-      <x:c r="B10" s="6" t="str"/>
+      <x:c r="B10" s="6"/>
       <x:c r="C10" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
         <x:v>リスクを知りたい</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
         <x:v>期待値ズレ</x:v>
@@ -588,24 +595,24 @@
       <x:c r="H10" s="6" t="str">
         <x:v>確認</x:v>
       </x:c>
-      <x:c r="I10" s="6" t="str"/>
+      <x:c r="I10" s="6"/>
     </x:row>
     <x:row r="11" ht="33" hidden="0" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>過去の経緯</x:v>
       </x:c>
-      <x:c r="B11" s="6" t="str"/>
+      <x:c r="B11" s="6"/>
       <x:c r="C11" s="6" t="str">
-        <x:v>If any</x:v>
+        <x:v>あれば</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
         <x:v>一度口頭で合意済み</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
         <x:v>事実誤認</x:v>
@@ -613,24 +620,24 @@
       <x:c r="H11" s="6" t="str">
         <x:v>確認</x:v>
       </x:c>
-      <x:c r="I11" s="6" t="str"/>
+      <x:c r="I11" s="6"/>
     </x:row>
     <x:row r="12" ht="33" hidden="0" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>地域/管轄</x:v>
       </x:c>
-      <x:c r="B12" s="6" t="str"/>
+      <x:c r="B12" s="6"/>
       <x:c r="C12" s="6" t="str">
-        <x:v>If relevant</x:v>
+        <x:v>必要なら</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
         <x:v>東京都</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
         <x:v>制度差</x:v>
@@ -638,24 +645,24 @@
       <x:c r="H12" s="6" t="str">
         <x:v>確認</x:v>
       </x:c>
-      <x:c r="I12" s="6" t="str"/>
+      <x:c r="I12" s="6"/>
     </x:row>
     <x:row r="13" ht="33" hidden="0" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>既存顧問の有無</x:v>
       </x:c>
-      <x:c r="B13" s="6" t="str"/>
+      <x:c r="B13" s="6"/>
       <x:c r="C13" s="6" t="str">
-        <x:v>If relevant</x:v>
+        <x:v>必要なら</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
         <x:v>なし</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
         <x:v>関係整理</x:v>
@@ -663,24 +670,24 @@
       <x:c r="H13" s="6" t="str">
         <x:v>確認</x:v>
       </x:c>
-      <x:c r="I13" s="6" t="str"/>
+      <x:c r="I13" s="6"/>
     </x:row>
     <x:row r="14" ht="33" hidden="0" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>緊急度</x:v>
       </x:c>
-      <x:c r="B14" s="6" t="str"/>
+      <x:c r="B14" s="6"/>
       <x:c r="C14" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
         <x:v>高/中/低</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F14" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
         <x:v>優先度ミス</x:v>
@@ -688,24 +695,24 @@
       <x:c r="H14" s="6" t="str">
         <x:v>分類</x:v>
       </x:c>
-      <x:c r="I14" s="6" t="str"/>
+      <x:c r="I14" s="6"/>
     </x:row>
     <x:row r="15" ht="33" hidden="0" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>対応可否メモ</x:v>
       </x:c>
-      <x:c r="B15" s="6" t="str"/>
+      <x:c r="B15" s="6"/>
       <x:c r="C15" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
         <x:v>専門外なら紹介</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F15" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
         <x:v>不適切受任</x:v>
@@ -713,24 +720,24 @@
       <x:c r="H15" s="6" t="str">
         <x:v>判断</x:v>
       </x:c>
-      <x:c r="I15" s="6" t="str"/>
+      <x:c r="I15" s="6"/>
     </x:row>
     <x:row r="16" ht="33" hidden="0" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>初回相談形式</x:v>
       </x:c>
-      <x:c r="B16" s="6" t="str"/>
+      <x:c r="B16" s="6"/>
       <x:c r="C16" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D16" s="6" t="str">
         <x:v>Zoom/対面/メール</x:v>
       </x:c>
       <x:c r="E16" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F16" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G16" s="6" t="str">
         <x:v>案内ミス</x:v>
@@ -738,24 +745,24 @@
       <x:c r="H16" s="6" t="str">
         <x:v>案内</x:v>
       </x:c>
-      <x:c r="I16" s="6" t="str"/>
+      <x:c r="I16" s="6"/>
     </x:row>
     <x:row r="17" ht="33" hidden="0" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>見積前提</x:v>
       </x:c>
-      <x:c r="B17" s="6" t="str"/>
+      <x:c r="B17" s="6"/>
       <x:c r="C17" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
         <x:v>資料確認後</x:v>
       </x:c>
       <x:c r="E17" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F17" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G17" s="6" t="str">
         <x:v>料金トラブル</x:v>
@@ -763,24 +770,24 @@
       <x:c r="H17" s="6" t="str">
         <x:v>注意</x:v>
       </x:c>
-      <x:c r="I17" s="6" t="str"/>
+      <x:c r="I17" s="6"/>
     </x:row>
     <x:row r="18" ht="33" hidden="0" customHeight="1">
       <x:c r="A18" s="6" t="str">
         <x:v>個人情報/機密</x:v>
       </x:c>
-      <x:c r="B18" s="6" t="str"/>
+      <x:c r="B18" s="6"/>
       <x:c r="C18" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D18" s="6" t="str">
         <x:v>含む</x:v>
       </x:c>
       <x:c r="E18" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F18" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G18" s="6" t="str">
         <x:v>漏えい</x:v>
@@ -788,7 +795,7 @@
       <x:c r="H18" s="6" t="str">
         <x:v>取り扱い注意</x:v>
       </x:c>
-      <x:c r="I18" s="6" t="str"/>
+      <x:c r="I18" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -811,28 +818,28 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Signal</x:v>
+        <x:v>兆候</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Likely Route</x:v>
+        <x:v>想定ルート</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Reason</x:v>
+        <x:v>理由</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Need More Info</x:v>
+        <x:v>追加確認</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Reply Tone</x:v>
+        <x:v>返信トーン</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Do Not Say</x:v>
+        <x:v>言わないこと</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Human Decision</x:v>
+        <x:v>人の判断</x:v>
       </x:c>
       <x:c r="H1" s="11" t="str">
-        <x:v>Example</x:v>
+        <x:v>例</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1115,25 +1122,25 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Section</x:v>
+        <x:v>区分</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Question</x:v>
+        <x:v>質問</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Why It Matters</x:v>
+        <x:v>重要な理由</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Ask Before Meeting?</x:v>
+        <x:v>面談前に聞く?</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Bring To Meeting</x:v>
+        <x:v>面談に持参</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>AI Can Prepare?</x:v>
+        <x:v>AIが準備可?</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Human Check</x:v>
+        <x:v>人の確認</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1147,13 +1154,13 @@
         <x:v>論点整理</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
         <x:v>時系列メモ</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
         <x:v>事実確認</x:v>
@@ -1170,13 +1177,13 @@
         <x:v>期待値調整</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
         <x:v>ゴール</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
         <x:v>現実性</x:v>
@@ -1193,13 +1200,13 @@
         <x:v>優先度</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
         <x:v>期限</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str">
         <x:v>対応可否</x:v>
@@ -1216,13 +1223,13 @@
         <x:v>判断前提</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
         <x:v>資料リスト</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
         <x:v>不足確認</x:v>
@@ -1239,13 +1246,13 @@
         <x:v>利益相反</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
         <x:v>関係者一覧</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="G6" s="6" t="str">
         <x:v>受任可否</x:v>
@@ -1262,13 +1269,13 @@
         <x:v>重要度</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
-        <x:v>If relevant</x:v>
+        <x:v>必要なら</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
         <x:v>金額</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
         <x:v>見積</x:v>
@@ -1285,13 +1292,13 @@
         <x:v>重複/方針</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>If any</x:v>
+        <x:v>あれば</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
         <x:v>過去回答</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
         <x:v>整合性</x:v>
@@ -1308,13 +1315,13 @@
         <x:v>方針</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
         <x:v>避けたい結果</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G9" s="6" t="str">
         <x:v>専門判断</x:v>
@@ -1331,13 +1338,13 @@
         <x:v>提案範囲</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
-        <x:v>Optional</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
         <x:v>予算</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
         <x:v>料金案内</x:v>
@@ -1354,13 +1361,13 @@
         <x:v>提案</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>Optional</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
         <x:v>頻度</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
         <x:v>契約条件</x:v>
@@ -1377,13 +1384,13 @@
         <x:v>安全</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
         <x:v>取り扱い</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
         <x:v>管理</x:v>
@@ -1400,13 +1407,13 @@
         <x:v>会議設計</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
         <x:v>意思決定</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
         <x:v>結論</x:v>
@@ -1430,19 +1437,19 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Reply Type</x:v>
+        <x:v>返信種別</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Use When</x:v>
+        <x:v>使う場面</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Structure</x:v>
+        <x:v>構成</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Include</x:v>
+        <x:v>入れること</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Avoid</x:v>
+        <x:v>避けること</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1600,22 +1607,22 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>AI Must Not Decide</x:v>
+        <x:v>AIに判断させないこと</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Why</x:v>
+        <x:v>理由</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Allowed AI Role</x:v>
+        <x:v>AIに許す役割</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Human Owner</x:v>
+        <x:v>人の責任者</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Safe Phrase</x:v>
+        <x:v>安全な表現</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Risky Phrase</x:v>
+        <x:v>危ない表現</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1855,16 +1862,16 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Prompt</x:v>
+        <x:v>プロンプト</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Use</x:v>
+        <x:v>用途</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Text</x:v>
+        <x:v>本文</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Human Check</x:v>
+        <x:v>人の確認</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
